--- a/frontend/test_guests.xlsx
+++ b/frontend/test_guests.xlsx
@@ -1,41 +1,362 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\aran\undangan\frontend\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52F92145-4910-4B7A-B9A9-B476D1099871}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Daftar Tamu" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="110">
+  <si>
+    <t>Nama Lengkap</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Rizka Amalia Nur Sulastri, S.KM.</t>
+  </si>
+  <si>
+    <t>Evi Puspa Ratri, S.Sos.</t>
+  </si>
+  <si>
+    <t>Rini Ulfa, SM.</t>
+  </si>
+  <si>
+    <t>Siti Syarah Harahap, S.Kom. &amp; Suami</t>
+  </si>
+  <si>
+    <t>Anggraini Nur Hadra, SM., MM.</t>
+  </si>
+  <si>
+    <t>Yusniar, A.md.Keb.</t>
+  </si>
+  <si>
+    <t>Muhammad Syawal Syahbirin, S.Sos.</t>
+  </si>
+  <si>
+    <t>Muh. Awal Radjani</t>
+  </si>
+  <si>
+    <t>Riyan Fitrah, S.Pd.</t>
+  </si>
+  <si>
+    <t>Muhammad Taufik Alrasyid</t>
+  </si>
+  <si>
+    <t>Hamzar</t>
+  </si>
+  <si>
+    <t>Fakhira Maritza, S.Pd.</t>
+  </si>
+  <si>
+    <t>Renaldi Tampila</t>
+  </si>
+  <si>
+    <t>Suryaningsih, S.P.</t>
+  </si>
+  <si>
+    <t>Rianinda Aprilia Sapitri, S.P.</t>
+  </si>
+  <si>
+    <t>Andi Lara Maulidha, S.P. &amp; Suami</t>
+  </si>
+  <si>
+    <t>Andi Tenri Ampa, S.P.</t>
+  </si>
+  <si>
+    <t>Fitraeni Nurdima Amiluddin, S.P.</t>
+  </si>
+  <si>
+    <t>Nur Azizah, S.P. &amp; Partner</t>
+  </si>
+  <si>
+    <t>Agnida Noviana Gowa Baharuddin, S.P.</t>
+  </si>
+  <si>
+    <t>Deasy Natalie Marten, S.P.</t>
+  </si>
+  <si>
+    <t>Feby Dwiamanda, S.P.</t>
+  </si>
+  <si>
+    <t>Nada Almaida Ali, S.P.</t>
+  </si>
+  <si>
+    <t>Ardista Riskyana Cantika, S.P</t>
+  </si>
+  <si>
+    <t>Ernawati Purba, S.P.</t>
+  </si>
+  <si>
+    <t>Gratianti Plena Serang, S.P.</t>
+  </si>
+  <si>
+    <t>Akmal, S.P.</t>
+  </si>
+  <si>
+    <t>Rezky Jaya</t>
+  </si>
+  <si>
+    <t>Rara dan Partner</t>
+  </si>
+  <si>
+    <t>Siti Masita, S.P</t>
+  </si>
+  <si>
+    <t>Ahmad Nur Azhari Dussy, S.P.</t>
+  </si>
+  <si>
+    <t>Berlin Mantung, S.P.</t>
+  </si>
+  <si>
+    <t>Fatur Rahman, S.P.</t>
+  </si>
+  <si>
+    <t>Intan Misi Amaliah, S.E.</t>
+  </si>
+  <si>
+    <t>Apt. Bintang Berlian, S.Farm.</t>
+  </si>
+  <si>
+    <t>Farida Ridwan</t>
+  </si>
+  <si>
+    <t>Nur kamaliyah Putri, S.Kg.</t>
+  </si>
+  <si>
+    <t>Puja Mutmainna, S.P. &amp; Suami</t>
+  </si>
+  <si>
+    <t>Siti Yulianti, S.P.</t>
+  </si>
+  <si>
+    <t>Prisky Dwi Praja, S.Farm.</t>
+  </si>
+  <si>
+    <t>Nur anisah, S.M. &amp; Suami</t>
+  </si>
+  <si>
+    <t>Syafina, S.KM.</t>
+  </si>
+  <si>
+    <t>Nadyah Syafni Fahira, S.P.</t>
+  </si>
+  <si>
+    <t>Dimas Muhammad Taufik, S.P., M.P.</t>
+  </si>
+  <si>
+    <t>Rahman, S.P.</t>
+  </si>
+  <si>
+    <t>Sri Wahyuni, S.P.</t>
+  </si>
+  <si>
+    <t>Tati Karmila, S.P.</t>
+  </si>
+  <si>
+    <t>Muliani &amp; Suami</t>
+  </si>
+  <si>
+    <t>Devi Oktaviani Moita</t>
+  </si>
+  <si>
+    <t>Ayu Andini Novitasari, SH.</t>
+  </si>
+  <si>
+    <t>Desianti, S.P.</t>
+  </si>
+  <si>
+    <t>Ir. Annisa Puji Lestari, Thahir, S.T., M.Eng.</t>
+  </si>
+  <si>
+    <t>Muhammad Zulfikar Gazali</t>
+  </si>
+  <si>
+    <t>Nur Namri Assiyaasah B.B.A</t>
+  </si>
+  <si>
+    <t>Prayogi Adi Laksono</t>
+  </si>
+  <si>
+    <t>Muhammad Artha Dwi Yanto, S.T.</t>
+  </si>
+  <si>
+    <t>Haris Fajar Setia Wibawa</t>
+  </si>
+  <si>
+    <t>Fathan Iliwua Yogansyah Taridala</t>
+  </si>
+  <si>
+    <t>M. Habibirrahman, A.A., S.Pd.</t>
+  </si>
+  <si>
+    <t>Muhammad Yusuf Syafaat, S.P.</t>
+  </si>
+  <si>
+    <t>Muhammad Israkin S.P.</t>
+  </si>
+  <si>
+    <t>Fadel Muhammad Saleh, S.P.</t>
+  </si>
+  <si>
+    <t>Muhammad Rafli, S.T.</t>
+  </si>
+  <si>
+    <t>La Ode Muhammad Nasrullah Eda, S.P.</t>
+  </si>
+  <si>
+    <t>Agung Setiawan, S.P.</t>
+  </si>
+  <si>
+    <t>Mohamad Alfi Nanda Laksana, S.P.</t>
+  </si>
+  <si>
+    <t>Abimanyu Galuh Prayoga, S.P.</t>
+  </si>
+  <si>
+    <t>I Putu Gede Mahendra, S.P.</t>
+  </si>
+  <si>
+    <t>Andri Jaya Amiruddin, S.P.</t>
+  </si>
+  <si>
+    <t>Hadi Riyandi, S.P.</t>
+  </si>
+  <si>
+    <t>Iful, S.P.</t>
+  </si>
+  <si>
+    <t>Arjun Ashar, S.P.</t>
+  </si>
+  <si>
+    <t>I Komang Wahyu, S.P.</t>
+  </si>
+  <si>
+    <t>Satria, S.P.</t>
+  </si>
+  <si>
+    <t>Muh Ikbal a.s S.T.</t>
+  </si>
+  <si>
+    <t>Aditya Prismawardana</t>
+  </si>
+  <si>
+    <t>Aldi</t>
+  </si>
+  <si>
+    <t>Anang Sofi Hergiman</t>
+  </si>
+  <si>
+    <t>Dewi Sarniati</t>
+  </si>
+  <si>
+    <t>Radju Wono Sakti</t>
+  </si>
+  <si>
+    <t>La Ode Abdul Rahman, S.M., M.M.</t>
+  </si>
+  <si>
+    <t>Ahmad Maulana, S.Pd.</t>
+  </si>
+  <si>
+    <t>Jalal Aminuddin</t>
+  </si>
+  <si>
+    <t>Nirdahayu, S.P.</t>
+  </si>
+  <si>
+    <t>Haidil Hamid, S.Pd.</t>
+  </si>
+  <si>
+    <t>Ernawati, S.P.</t>
+  </si>
+  <si>
+    <t>I Kadek Pande Prasetia W</t>
+  </si>
+  <si>
+    <t>Dyna Indah Lestari H, S.P.</t>
+  </si>
+  <si>
+    <t>Sri dan umar</t>
+  </si>
+  <si>
+    <t>Muhammad Ilham Rasyid, S.E.</t>
+  </si>
+  <si>
+    <t>Ida Bagus Putu Surya Adnyana</t>
+  </si>
+  <si>
+    <t>Seren Elfitriani, S.P.</t>
+  </si>
+  <si>
+    <t>Muhammad Al Latif Permana</t>
+  </si>
+  <si>
+    <t>Dzaky Ahmad Dzakhilullah</t>
+  </si>
+  <si>
+    <t>Muh. Fajij Fadillah Ambo</t>
+  </si>
+  <si>
+    <t>Surya Herlambang</t>
+  </si>
+  <si>
+    <t>Diyas Rafliansyah</t>
+  </si>
+  <si>
+    <t>Ivan Heldi A.P</t>
+  </si>
+  <si>
+    <t>Andi Dhesta Adhytia Yusuf</t>
+  </si>
+  <si>
+    <t>Muh. Nazar</t>
+  </si>
+  <si>
+    <t>Ahmad</t>
+  </si>
+  <si>
+    <t>Abdul Rahman</t>
+  </si>
+  <si>
+    <t>Nikita Gedalya Yonas</t>
+  </si>
+  <si>
+    <t>Siti Rahma Savira Azzuhra</t>
+  </si>
+  <si>
+    <t>Ryan Rudi Rusanto, S.P.</t>
+  </si>
+  <si>
+    <t>Asyraf Fawwaz, S.H., M.H.</t>
+  </si>
+  <si>
+    <t>Fitriyah Dwi Rahma, ST</t>
+  </si>
+  <si>
+    <t>Muhammad Amin Saleh Al Habsy</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -65,13 +386,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,60 +725,570 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B110"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="35.5" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Nama Lengkap</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Status</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Bapak Ahmad Santoso &amp; Ibu Siti Aminah</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Belum Konfirmasi</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Keluarga Besar Putri</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Konfirmasi Hadir</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Citra Saraswati</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Belum Konfirmasi</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Steven William</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Konfirmasi Hadir</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Dr. Hendra Wijaya, Sp.PD</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Belum Konfirmasi</v>
+    <row r="1" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B6"/>
+    <ignoredError sqref="A1:B1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>